--- a/data/NON_IR_Register_DGGI_MZU_upto_09_July_2026.xlsx
+++ b/data/NON_IR_Register_DGGI_MZU_upto_09_July_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cbicmof-my.sharepoint.com/personal/10058814_cbic_gov_in/Documents/Documents/Copilot/Created/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A07BC47-3CB1-42A5-887E-8D2DCCFE25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{8A07BC47-3CB1-42A5-887E-8D2DCCFE25DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BCB6B6B-6CA4-4ABB-90ED-B7819BA9CDFF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="Source" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="289">
   <si>
     <t>Sr No</t>
   </si>
@@ -895,6 +894,18 @@
   </si>
   <si>
     <t>E-Mail ID</t>
+  </si>
+  <si>
+    <t>DGGI/INT/INTL/454/2026-Gr D-O/o Pr. ADG-DGGI-ZU-MUMBAI-Part I</t>
+  </si>
+  <si>
+    <t>DGGI/INT/INTL/227/2026-Gr C-O/o Pr. ADG-DGGI-ZU-MUMBAI-Part I</t>
+  </si>
+  <si>
+    <t>DGGI/INV/GST/996/2026-Gr C-O/o Pr. ADG-DGGI-ZU-MUMBAI</t>
+  </si>
+  <si>
+    <t>DGGI/INV/GST/994/2026-Gr C-O/o Pr. ADG-DGGI-ZU-MUMBAI</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1019,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1043,10 +1064,10 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{46EE34BF-582B-4D61-A1E1-78D5E0F33AC3}" name="Sr No" dataCellStyle="Normal"/>
     <tableColumn id="2" xr3:uid="{DCC2EFEA-0A10-42FE-8354-F924764C1B17}" name="File Number" dataCellStyle="Normal"/>
-    <tableColumn id="3" xr3:uid="{0FDD96A6-3BE5-4A19-94E9-F0ED4B677221}" name="Date of NON-IR" dataDxfId="1" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{0FDD96A6-3BE5-4A19-94E9-F0ED4B677221}" name="Date of NON-IR" dataDxfId="4" dataCellStyle="Normal"/>
     <tableColumn id="4" xr3:uid="{10D93C50-FBFF-42D6-96CE-8D5E1AB308E1}" name="Officer Name" dataCellStyle="Normal"/>
     <tableColumn id="5" xr3:uid="{1B562F4D-C716-476D-B0D6-75B4B23A6CA6}" name="Group Name" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{538BE97B-83D5-40C6-B949-95828D6284A2}" name="E-Mail ID" dataDxfId="0" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{538BE97B-83D5-40C6-B949-95828D6284A2}" name="E-Mail ID" dataDxfId="3" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1067,10 +1088,10 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr No" dataCellStyle="Normal"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="File Number" dataCellStyle="Normal"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Date of NON-IR" dataDxfId="3" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Date of NON-IR" dataDxfId="2" dataCellStyle="Normal"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Officer Name" dataCellStyle="Normal"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Group Name" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{E0E77D03-092A-4D9F-AE6F-22FBDEB3CDDE}" name="E-Mail ID" dataDxfId="2" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{E0E77D03-092A-4D9F-AE6F-22FBDEB3CDDE}" name="E-Mail ID" dataDxfId="1" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2260,7 +2281,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>286</v>
       </c>
       <c r="C45" s="6">
         <v>46080</v>
@@ -2540,7 +2561,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>287</v>
       </c>
       <c r="C59" s="6">
         <v>46114</v>
@@ -2560,7 +2581,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="C60" s="6">
         <v>46114</v>
@@ -3240,7 +3261,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>99</v>
+        <v>285</v>
       </c>
       <c r="C94" s="6">
         <v>46167</v>
@@ -3957,6 +3978,9 @@
     </row>
     <row r="131" spans="1:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="11" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
